--- a/data/trans_orig/P25F_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023</t>
+          <t>Población según el modo de empleo para el que utilizan los cigarrillos electrónicos en 2023 (tasa de respuesta: 90,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10393</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>14667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27170</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47821</t>
+          <t>48104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20798</t>
+          <t>19245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>22877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17287</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>23539</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26928</t>
+          <t>24829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>905</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>62,44%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>63,01%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,52%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>72,55%</t>
         </is>
       </c>
     </row>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4970,62 +4970,62 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>66550</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>48463</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>84055</t>
+          <t>84908</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>30571</t>
+          <t>30126</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>26126</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>53235</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25F_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P25F_2023-Edad-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -838,27 +838,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30167</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35921</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14667</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>39726</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>29418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48104</t>
+          <t>50951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6143</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>10830</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22877</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>40,76%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35921</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35921</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35921</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>23105</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>53291</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>53291</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53291</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>21634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18391</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>14445</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7812</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>26515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>880</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24829</t>
+          <t>27225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,77%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32986</t>
+          <t>36776</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32986</t>
+          <t>36776</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32986</t>
+          <t>36776</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>48232</t>
+          <t>52593</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>48232</t>
+          <t>52593</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>48232</t>
+          <t>52593</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7626</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>794</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>19488</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19488</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19488</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>456</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>60,51%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>10726</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,27 +3940,27 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>610</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>610</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>919</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>919</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>919</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>52694</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>36655</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>63793</t>
+          <t>67000</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>64279</t>
+          <t>69762</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>48463</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>84908</t>
+          <t>88732</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>17988</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>31242</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>17170</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>30126</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>20793</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>35994</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>20303</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>26933</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>99719</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>55989</t>
+          <t>65995</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>155708</t>
+          <t>174555</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
